--- a/docs/informes/edistribucion_demanda_2026-10-02.xlsx
+++ b/docs/informes/edistribucion_demanda_2026-10-02.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026 08:11</t>
+          <t>02/10/2026 09:56</t>
         </is>
       </c>
     </row>

--- a/docs/informes/edistribucion_demanda_2026-10-02.xlsx
+++ b/docs/informes/edistribucion_demanda_2026-10-02.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026 09:56</t>
+          <t>02/10/2026 12:44</t>
         </is>
       </c>
     </row>

--- a/docs/informes/edistribucion_demanda_2026-10-02.xlsx
+++ b/docs/informes/edistribucion_demanda_2026-10-02.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026 12:44</t>
+          <t>02/10/2026 13:57</t>
         </is>
       </c>
     </row>
